--- a/config/Amazon_instruction.xlsx
+++ b/config/Amazon_instruction.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\our data\KPA\NEW\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB12BA1A-3B90-4067-B3BF-EBB0C454F4BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8308C76-9561-4335-885D-F60CF4D1311B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="256">
   <si>
     <t>Base file Column</t>
   </si>
@@ -1170,11 +1170,17 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>1</v>
+      </c>
       <c r="B4" t="s">
         <v>5</v>
       </c>
       <c r="C4" t="s">
         <v>255</v>
+      </c>
+      <c r="D4" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -1198,6 +1204,9 @@
       <c r="C6" t="s">
         <v>255</v>
       </c>
+      <c r="D6" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
@@ -1220,6 +1229,9 @@
       <c r="C8" t="s">
         <v>255</v>
       </c>
+      <c r="D8" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
@@ -1452,7 +1464,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>226</v>
       </c>
@@ -1463,7 +1475,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>227</v>
       </c>
@@ -1474,7 +1486,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>228</v>
       </c>
@@ -1485,7 +1497,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B36" t="s">
         <v>37</v>
       </c>
@@ -1493,7 +1505,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B37" t="s">
         <v>38</v>
       </c>
@@ -1501,7 +1513,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B38" t="s">
         <v>39</v>
       </c>
@@ -1509,7 +1521,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B39" t="s">
         <v>40</v>
       </c>
@@ -1517,7 +1529,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B40" t="s">
         <v>41</v>
       </c>
@@ -1525,7 +1537,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B41" t="s">
         <v>42</v>
       </c>
@@ -1533,7 +1545,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>229</v>
       </c>
@@ -1544,7 +1556,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>1</v>
       </c>
@@ -1554,8 +1566,11 @@
       <c r="C43" t="s">
         <v>255</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D43" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B44" t="s">
         <v>45</v>
       </c>
@@ -1563,7 +1578,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B45" t="s">
         <v>46</v>
       </c>
@@ -1571,7 +1586,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B46" t="s">
         <v>47</v>
       </c>
@@ -1579,7 +1594,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B47" t="s">
         <v>48</v>
       </c>
@@ -1587,7 +1602,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>1</v>
       </c>
@@ -1596,6 +1611,9 @@
       </c>
       <c r="C48" t="s">
         <v>255</v>
+      </c>
+      <c r="D48" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
@@ -1640,6 +1658,9 @@
       <c r="C53" t="s">
         <v>255</v>
       </c>
+      <c r="D53" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
@@ -1743,6 +1764,9 @@
       <c r="C61" t="s">
         <v>255</v>
       </c>
+      <c r="D61" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
@@ -1831,6 +1855,9 @@
       <c r="C69" t="s">
         <v>255</v>
       </c>
+      <c r="D69" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
@@ -2031,6 +2058,9 @@
       <c r="C88" t="s">
         <v>255</v>
       </c>
+      <c r="D88" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B89" t="s">
@@ -2050,6 +2080,9 @@
       <c r="C90" t="s">
         <v>255</v>
       </c>
+      <c r="D90" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B91" t="s">
@@ -2157,6 +2190,9 @@
       <c r="C103" t="s">
         <v>255</v>
       </c>
+      <c r="D103" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
@@ -2239,7 +2275,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B113" t="s">
         <v>113</v>
       </c>
@@ -2247,7 +2283,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B114" t="s">
         <v>114</v>
       </c>
@@ -2255,7 +2291,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B115" t="s">
         <v>115</v>
       </c>
@@ -2263,7 +2299,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B116" t="s">
         <v>116</v>
       </c>
@@ -2271,7 +2307,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B117" t="s">
         <v>117</v>
       </c>
@@ -2279,7 +2315,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B118" t="s">
         <v>118</v>
       </c>
@@ -2287,7 +2323,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B119" t="s">
         <v>119</v>
       </c>
@@ -2295,7 +2331,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>1</v>
       </c>
@@ -2305,8 +2341,11 @@
       <c r="C120" t="s">
         <v>255</v>
       </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D120" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>1</v>
       </c>
@@ -2316,8 +2355,11 @@
       <c r="C121" t="s">
         <v>255</v>
       </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D121" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B122" t="s">
         <v>122</v>
       </c>
@@ -2325,7 +2367,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B123" t="s">
         <v>123</v>
       </c>
@@ -2333,7 +2375,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B124" t="s">
         <v>124</v>
       </c>
@@ -2341,7 +2383,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B125" t="s">
         <v>125</v>
       </c>
@@ -2349,7 +2391,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B126" t="s">
         <v>126</v>
       </c>
@@ -2357,7 +2399,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B127" t="s">
         <v>127</v>
       </c>
@@ -2365,7 +2407,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>219</v>
       </c>
@@ -2426,6 +2468,9 @@
       <c r="C134" t="s">
         <v>255</v>
       </c>
+      <c r="D134" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B135" t="s">
@@ -2475,6 +2520,9 @@
       <c r="C139" t="s">
         <v>255</v>
       </c>
+      <c r="D139" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B140" t="s">
@@ -2650,7 +2698,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>1</v>
       </c>
@@ -2660,8 +2708,11 @@
       <c r="C161" t="s">
         <v>255</v>
       </c>
-    </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D161" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>249</v>
       </c>
@@ -2672,7 +2723,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>1</v>
       </c>
@@ -2682,8 +2733,11 @@
       <c r="C163" t="s">
         <v>255</v>
       </c>
-    </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D163" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>250</v>
       </c>
@@ -2694,7 +2748,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>1</v>
       </c>
@@ -2704,8 +2758,11 @@
       <c r="C165" t="s">
         <v>255</v>
       </c>
-    </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D165" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>248</v>
       </c>
@@ -2716,7 +2773,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>1</v>
       </c>
@@ -2726,8 +2783,11 @@
       <c r="C167" t="s">
         <v>255</v>
       </c>
-    </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D167" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>249</v>
       </c>
@@ -2738,7 +2798,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>1</v>
       </c>
@@ -2748,8 +2808,11 @@
       <c r="C169" t="s">
         <v>255</v>
       </c>
-    </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D169" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>250</v>
       </c>
@@ -2760,7 +2823,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>1</v>
       </c>
@@ -2770,8 +2833,11 @@
       <c r="C171" t="s">
         <v>255</v>
       </c>
-    </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D171" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>251</v>
       </c>
@@ -2782,7 +2848,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>1</v>
       </c>
@@ -2792,8 +2858,11 @@
       <c r="C173" t="s">
         <v>255</v>
       </c>
-    </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D173" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>1</v>
       </c>
@@ -2803,8 +2872,11 @@
       <c r="C174" t="s">
         <v>255</v>
       </c>
-    </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D174" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>233</v>
       </c>
@@ -2815,7 +2887,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>252</v>
       </c>
@@ -2826,7 +2898,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>251</v>
       </c>
@@ -2837,7 +2909,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>1</v>
       </c>
@@ -2847,8 +2919,11 @@
       <c r="C178" t="s">
         <v>255</v>
       </c>
-    </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D178" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B179" t="s">
         <v>179</v>
       </c>
@@ -2856,7 +2931,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B180" t="s">
         <v>180</v>
       </c>
@@ -2864,7 +2939,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B181" t="s">
         <v>181</v>
       </c>
@@ -2872,7 +2947,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B182" t="s">
         <v>182</v>
       </c>
@@ -2880,7 +2955,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B183" t="s">
         <v>183</v>
       </c>
@@ -2888,7 +2963,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B184" t="s">
         <v>184</v>
       </c>
@@ -2896,7 +2971,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B185" t="s">
         <v>185</v>
       </c>
@@ -2904,7 +2979,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B186" t="s">
         <v>186</v>
       </c>
@@ -2912,7 +2987,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B187" t="s">
         <v>187</v>
       </c>
@@ -2920,7 +2995,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B188" t="s">
         <v>188</v>
       </c>
@@ -2928,7 +3003,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B189" t="s">
         <v>189</v>
       </c>
@@ -2936,7 +3011,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B190" t="s">
         <v>190</v>
       </c>
@@ -2944,7 +3019,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B191" t="s">
         <v>191</v>
       </c>
@@ -2952,7 +3027,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B192" t="s">
         <v>192</v>
       </c>

--- a/config/Amazon_instruction.xlsx
+++ b/config/Amazon_instruction.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\our data\KPA\NEW\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8308C76-9561-4335-885D-F60CF4D1311B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A29E8DFD-6288-4B3D-A453-48FAF6AE9BEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Mapping-Tshirts" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mapping-Tshirts'!$A$1:$E$210</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mapping-Tshirts'!$A$1:$E$211</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="257">
   <si>
     <t>Base file Column</t>
   </si>
@@ -807,6 +807,9 @@
   </si>
   <si>
     <t>Tshirts</t>
+  </si>
+  <si>
+    <t>item_booking_date#1.value</t>
   </si>
 </sst>
 </file>
@@ -1124,7 +1127,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E210"/>
+  <dimension ref="A1:E211"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.7265625" bestFit="1" customWidth="1"/>
@@ -1921,30 +1924,30 @@
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A75" t="s">
+      <c r="B75" t="s">
+        <v>256</v>
+      </c>
+      <c r="C75" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
         <v>241</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B76" t="s">
         <v>81</v>
       </c>
-      <c r="C75" t="s">
-        <v>255</v>
-      </c>
-      <c r="D75" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B76" t="s">
-        <v>76</v>
-      </c>
       <c r="C76" t="s">
         <v>255</v>
+      </c>
+      <c r="D76" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B77" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C77" t="s">
         <v>255</v>
@@ -1952,7 +1955,7 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B78" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C78" t="s">
         <v>255</v>
@@ -1960,7 +1963,7 @@
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B79" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C79" t="s">
         <v>255</v>
@@ -1968,7 +1971,7 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B80" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C80" t="s">
         <v>255</v>
@@ -1976,7 +1979,7 @@
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B81" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C81" t="s">
         <v>255</v>
@@ -1984,117 +1987,117 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B82" t="s">
+        <v>81</v>
+      </c>
+      <c r="C82" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B83" t="s">
         <v>82</v>
       </c>
-      <c r="C82" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A83" t="s">
-        <v>242</v>
-      </c>
-      <c r="B83" t="s">
-        <v>83</v>
-      </c>
       <c r="C83" t="s">
         <v>255</v>
-      </c>
-      <c r="D83" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
+        <v>242</v>
+      </c>
+      <c r="B84" t="s">
+        <v>83</v>
+      </c>
+      <c r="C84" t="s">
+        <v>255</v>
+      </c>
+      <c r="D84" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
         <v>219</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B85" t="s">
         <v>84</v>
       </c>
-      <c r="C84" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B85" t="s">
+      <c r="C85" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B86" t="s">
         <v>85</v>
       </c>
-      <c r="C85" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A86" t="s">
-        <v>243</v>
-      </c>
-      <c r="B86" t="s">
-        <v>86</v>
-      </c>
       <c r="C86" t="s">
         <v>255</v>
-      </c>
-      <c r="D86" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="B87" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C87" t="s">
         <v>255</v>
+      </c>
+      <c r="D87" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
+        <v>233</v>
+      </c>
+      <c r="B88" t="s">
+        <v>87</v>
+      </c>
+      <c r="C88" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A89" t="s">
         <v>1</v>
       </c>
-      <c r="B88" t="s">
+      <c r="B89" t="s">
         <v>88</v>
       </c>
-      <c r="C88" t="s">
-        <v>255</v>
-      </c>
-      <c r="D88" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B89" t="s">
+      <c r="C89" t="s">
+        <v>255</v>
+      </c>
+      <c r="D89" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B90" t="s">
         <v>89</v>
       </c>
-      <c r="C89" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A90" t="s">
+      <c r="C90" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A91" t="s">
         <v>1</v>
       </c>
-      <c r="B90" t="s">
+      <c r="B91" t="s">
         <v>90</v>
       </c>
-      <c r="C90" t="s">
-        <v>255</v>
-      </c>
-      <c r="D90" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B91" t="s">
-        <v>91</v>
-      </c>
       <c r="C91" t="s">
         <v>255</v>
+      </c>
+      <c r="D91" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B92" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C92" t="s">
         <v>255</v>
@@ -2102,7 +2105,7 @@
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B93" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C93" t="s">
         <v>255</v>
@@ -2110,7 +2113,7 @@
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B94" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C94" t="s">
         <v>255</v>
@@ -2118,7 +2121,7 @@
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B95" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C95" t="s">
         <v>255</v>
@@ -2126,7 +2129,7 @@
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B96" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C96" t="s">
         <v>255</v>
@@ -2134,7 +2137,7 @@
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B97" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C97" t="s">
         <v>255</v>
@@ -2142,7 +2145,7 @@
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B98" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C98" t="s">
         <v>255</v>
@@ -2150,7 +2153,7 @@
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B99" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C99" t="s">
         <v>255</v>
@@ -2158,7 +2161,7 @@
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B100" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C100" t="s">
         <v>255</v>
@@ -2166,7 +2169,7 @@
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B101" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C101" t="s">
         <v>255</v>
@@ -2174,40 +2177,40 @@
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B102" t="s">
+        <v>101</v>
+      </c>
+      <c r="C102" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B103" t="s">
         <v>102</v>
       </c>
-      <c r="C102" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A103" t="s">
-        <v>1</v>
-      </c>
-      <c r="B103" t="s">
-        <v>103</v>
-      </c>
       <c r="C103" t="s">
         <v>255</v>
-      </c>
-      <c r="D103" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
+        <v>1</v>
+      </c>
+      <c r="B104" t="s">
+        <v>103</v>
+      </c>
+      <c r="C104" t="s">
+        <v>255</v>
+      </c>
+      <c r="D104" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A105" t="s">
         <v>244</v>
       </c>
-      <c r="B104" t="s">
+      <c r="B105" t="s">
         <v>104</v>
-      </c>
-      <c r="C104" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B105" t="s">
-        <v>105</v>
       </c>
       <c r="C105" t="s">
         <v>255</v>
@@ -2215,7 +2218,7 @@
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B106" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C106" t="s">
         <v>255</v>
@@ -2223,7 +2226,7 @@
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B107" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C107" t="s">
         <v>255</v>
@@ -2231,7 +2234,7 @@
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B108" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C108" t="s">
         <v>255</v>
@@ -2239,37 +2242,37 @@
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B109" t="s">
+        <v>108</v>
+      </c>
+      <c r="C109" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B110" t="s">
         <v>109</v>
       </c>
-      <c r="C109" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A110" t="s">
+      <c r="C110" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A111" t="s">
         <v>245</v>
       </c>
-      <c r="B110" t="s">
+      <c r="B111" t="s">
         <v>110</v>
       </c>
-      <c r="C110" t="s">
-        <v>255</v>
-      </c>
-      <c r="D110" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B111" t="s">
-        <v>111</v>
-      </c>
       <c r="C111" t="s">
         <v>255</v>
+      </c>
+      <c r="D111" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B112" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C112" t="s">
         <v>255</v>
@@ -2277,7 +2280,7 @@
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B113" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C113" t="s">
         <v>255</v>
@@ -2285,7 +2288,7 @@
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B114" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C114" t="s">
         <v>255</v>
@@ -2293,7 +2296,7 @@
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B115" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C115" t="s">
         <v>255</v>
@@ -2301,7 +2304,7 @@
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B116" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C116" t="s">
         <v>255</v>
@@ -2309,7 +2312,7 @@
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B117" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C117" t="s">
         <v>255</v>
@@ -2317,7 +2320,7 @@
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B118" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C118" t="s">
         <v>255</v>
@@ -2325,24 +2328,18 @@
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B119" t="s">
+        <v>118</v>
+      </c>
+      <c r="C119" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B120" t="s">
         <v>119</v>
       </c>
-      <c r="C119" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A120" t="s">
-        <v>1</v>
-      </c>
-      <c r="B120" t="s">
-        <v>120</v>
-      </c>
       <c r="C120" t="s">
         <v>255</v>
-      </c>
-      <c r="D120" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.35">
@@ -2350,26 +2347,32 @@
         <v>1</v>
       </c>
       <c r="B121" t="s">
+        <v>120</v>
+      </c>
+      <c r="C121" t="s">
+        <v>255</v>
+      </c>
+      <c r="D121" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A122" t="s">
+        <v>1</v>
+      </c>
+      <c r="B122" t="s">
         <v>121</v>
       </c>
-      <c r="C121" t="s">
-        <v>255</v>
-      </c>
-      <c r="D121" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B122" t="s">
-        <v>122</v>
-      </c>
       <c r="C122" t="s">
         <v>255</v>
+      </c>
+      <c r="D122" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B123" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C123" t="s">
         <v>255</v>
@@ -2377,7 +2380,7 @@
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B124" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C124" t="s">
         <v>255</v>
@@ -2385,7 +2388,7 @@
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B125" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C125" t="s">
         <v>255</v>
@@ -2393,7 +2396,7 @@
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B126" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C126" t="s">
         <v>255</v>
@@ -2401,26 +2404,26 @@
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B127" t="s">
+        <v>126</v>
+      </c>
+      <c r="C127" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B128" t="s">
         <v>127</v>
       </c>
-      <c r="C127" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A128" t="s">
+      <c r="C128" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A129" t="s">
         <v>219</v>
       </c>
-      <c r="B128" t="s">
+      <c r="B129" t="s">
         <v>128</v>
-      </c>
-      <c r="C128" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B129" t="s">
-        <v>129</v>
       </c>
       <c r="C129" t="s">
         <v>255</v>
@@ -2428,7 +2431,7 @@
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B130" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C130" t="s">
         <v>255</v>
@@ -2436,7 +2439,7 @@
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B131" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C131" t="s">
         <v>255</v>
@@ -2444,7 +2447,7 @@
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B132" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C132" t="s">
         <v>255</v>
@@ -2452,89 +2455,89 @@
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B133" t="s">
+        <v>132</v>
+      </c>
+      <c r="C133" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B134" t="s">
         <v>133</v>
       </c>
-      <c r="C133" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A134" t="s">
+      <c r="C134" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A135" t="s">
         <v>1</v>
       </c>
-      <c r="B134" t="s">
+      <c r="B135" t="s">
         <v>134</v>
       </c>
-      <c r="C134" t="s">
-        <v>255</v>
-      </c>
-      <c r="D134" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B135" t="s">
-        <v>135</v>
-      </c>
       <c r="C135" t="s">
         <v>255</v>
+      </c>
+      <c r="D135" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B136" t="s">
+        <v>135</v>
+      </c>
+      <c r="C136" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B137" t="s">
         <v>136</v>
       </c>
-      <c r="C136" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A137" t="s">
+      <c r="C137" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A138" t="s">
         <v>246</v>
       </c>
-      <c r="B137" t="s">
+      <c r="B138" t="s">
         <v>137</v>
       </c>
-      <c r="C137" t="s">
-        <v>255</v>
-      </c>
-      <c r="D137" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B138" t="s">
+      <c r="C138" t="s">
+        <v>255</v>
+      </c>
+      <c r="D138" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B139" t="s">
         <v>138</v>
       </c>
-      <c r="C138" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A139" t="s">
+      <c r="C139" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A140" t="s">
         <v>1</v>
       </c>
-      <c r="B139" t="s">
+      <c r="B140" t="s">
         <v>139</v>
       </c>
-      <c r="C139" t="s">
-        <v>255</v>
-      </c>
-      <c r="D139" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B140" t="s">
-        <v>140</v>
-      </c>
       <c r="C140" t="s">
         <v>255</v>
+      </c>
+      <c r="D140" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B141" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C141" t="s">
         <v>255</v>
@@ -2542,7 +2545,7 @@
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B142" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C142" t="s">
         <v>255</v>
@@ -2550,7 +2553,7 @@
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B143" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C143" t="s">
         <v>255</v>
@@ -2558,7 +2561,7 @@
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B144" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C144" t="s">
         <v>255</v>
@@ -2566,7 +2569,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B145" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C145" t="s">
         <v>255</v>
@@ -2574,7 +2577,7 @@
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B146" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C146" t="s">
         <v>255</v>
@@ -2582,7 +2585,7 @@
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B147" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C147" t="s">
         <v>255</v>
@@ -2590,7 +2593,7 @@
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B148" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C148" t="s">
         <v>255</v>
@@ -2598,7 +2601,7 @@
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B149" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C149" t="s">
         <v>255</v>
@@ -2606,7 +2609,7 @@
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B150" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C150" t="s">
         <v>255</v>
@@ -2614,7 +2617,7 @@
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B151" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C151" t="s">
         <v>255</v>
@@ -2622,7 +2625,7 @@
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B152" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C152" t="s">
         <v>255</v>
@@ -2630,7 +2633,7 @@
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B153" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C153" t="s">
         <v>255</v>
@@ -2638,7 +2641,7 @@
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B154" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C154" t="s">
         <v>255</v>
@@ -2646,7 +2649,7 @@
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B155" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C155" t="s">
         <v>255</v>
@@ -2654,26 +2657,26 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B156" t="s">
+        <v>155</v>
+      </c>
+      <c r="C156" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B157" t="s">
         <v>156</v>
       </c>
-      <c r="C156" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A157" t="s">
+      <c r="C157" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A158" t="s">
         <v>247</v>
       </c>
-      <c r="B157" t="s">
+      <c r="B158" t="s">
         <v>157</v>
-      </c>
-      <c r="C157" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B158" t="s">
-        <v>158</v>
       </c>
       <c r="C158" t="s">
         <v>255</v>
@@ -2681,18 +2684,15 @@
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B159" t="s">
+        <v>158</v>
+      </c>
+      <c r="C159" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B160" t="s">
         <v>159</v>
-      </c>
-      <c r="C159" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A160" t="s">
-        <v>248</v>
-      </c>
-      <c r="B160" t="s">
-        <v>160</v>
       </c>
       <c r="C160" t="s">
         <v>255</v>
@@ -2700,166 +2700,163 @@
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>1</v>
+        <v>248</v>
       </c>
       <c r="B161" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C161" t="s">
         <v>255</v>
-      </c>
-      <c r="D161" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>249</v>
+        <v>1</v>
       </c>
       <c r="B162" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C162" t="s">
         <v>255</v>
+      </c>
+      <c r="D162" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>1</v>
+        <v>249</v>
       </c>
       <c r="B163" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C163" t="s">
         <v>255</v>
-      </c>
-      <c r="D163" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>250</v>
+        <v>1</v>
       </c>
       <c r="B164" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C164" t="s">
         <v>255</v>
+      </c>
+      <c r="D164" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>1</v>
+        <v>250</v>
       </c>
       <c r="B165" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C165" t="s">
         <v>255</v>
-      </c>
-      <c r="D165" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>248</v>
+        <v>1</v>
       </c>
       <c r="B166" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C166" t="s">
         <v>255</v>
+      </c>
+      <c r="D166" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>1</v>
+        <v>248</v>
       </c>
       <c r="B167" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C167" t="s">
         <v>255</v>
-      </c>
-      <c r="D167" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>249</v>
+        <v>1</v>
       </c>
       <c r="B168" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C168" t="s">
         <v>255</v>
+      </c>
+      <c r="D168" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>1</v>
+        <v>249</v>
       </c>
       <c r="B169" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C169" t="s">
         <v>255</v>
-      </c>
-      <c r="D169" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
-        <v>250</v>
+        <v>1</v>
       </c>
       <c r="B170" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C170" t="s">
         <v>255</v>
+      </c>
+      <c r="D170" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
-        <v>1</v>
+        <v>250</v>
       </c>
       <c r="B171" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C171" t="s">
         <v>255</v>
-      </c>
-      <c r="D171" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
-        <v>251</v>
+        <v>1</v>
       </c>
       <c r="B172" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C172" t="s">
         <v>255</v>
+      </c>
+      <c r="D172" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
-        <v>1</v>
+        <v>251</v>
       </c>
       <c r="B173" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C173" t="s">
         <v>255</v>
-      </c>
-      <c r="D173" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.35">
@@ -2867,7 +2864,7 @@
         <v>1</v>
       </c>
       <c r="B174" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C174" t="s">
         <v>255</v>
@@ -2878,21 +2875,24 @@
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
-        <v>233</v>
+        <v>1</v>
       </c>
       <c r="B175" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C175" t="s">
         <v>255</v>
+      </c>
+      <c r="D175" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>252</v>
+        <v>233</v>
       </c>
       <c r="B176" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C176" t="s">
         <v>255</v>
@@ -2900,10 +2900,10 @@
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B177" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C177" t="s">
         <v>255</v>
@@ -2911,29 +2911,32 @@
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
+        <v>251</v>
+      </c>
+      <c r="B178" t="s">
+        <v>177</v>
+      </c>
+      <c r="C178" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A179" t="s">
         <v>1</v>
       </c>
-      <c r="B178" t="s">
+      <c r="B179" t="s">
         <v>178</v>
       </c>
-      <c r="C178" t="s">
-        <v>255</v>
-      </c>
-      <c r="D178" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B179" t="s">
-        <v>179</v>
-      </c>
       <c r="C179" t="s">
         <v>255</v>
+      </c>
+      <c r="D179" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B180" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C180" t="s">
         <v>255</v>
@@ -2941,7 +2944,7 @@
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B181" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C181" t="s">
         <v>255</v>
@@ -2949,7 +2952,7 @@
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B182" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C182" t="s">
         <v>255</v>
@@ -2957,7 +2960,7 @@
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B183" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C183" t="s">
         <v>255</v>
@@ -2965,7 +2968,7 @@
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B184" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C184" t="s">
         <v>255</v>
@@ -2973,7 +2976,7 @@
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B185" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C185" t="s">
         <v>255</v>
@@ -2981,7 +2984,7 @@
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B186" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C186" t="s">
         <v>255</v>
@@ -2989,7 +2992,7 @@
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B187" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C187" t="s">
         <v>255</v>
@@ -2997,7 +3000,7 @@
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B188" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C188" t="s">
         <v>255</v>
@@ -3005,7 +3008,7 @@
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B189" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C189" t="s">
         <v>255</v>
@@ -3013,7 +3016,7 @@
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B190" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C190" t="s">
         <v>255</v>
@@ -3021,7 +3024,7 @@
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B191" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C191" t="s">
         <v>255</v>
@@ -3029,7 +3032,7 @@
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B192" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C192" t="s">
         <v>255</v>
@@ -3037,7 +3040,7 @@
     </row>
     <row r="193" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B193" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C193" t="s">
         <v>255</v>
@@ -3045,7 +3048,7 @@
     </row>
     <row r="194" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B194" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C194" t="s">
         <v>255</v>
@@ -3053,7 +3056,7 @@
     </row>
     <row r="195" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B195" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C195" t="s">
         <v>255</v>
@@ -3061,7 +3064,7 @@
     </row>
     <row r="196" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B196" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C196" t="s">
         <v>255</v>
@@ -3069,7 +3072,7 @@
     </row>
     <row r="197" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B197" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C197" t="s">
         <v>255</v>
@@ -3077,7 +3080,7 @@
     </row>
     <row r="198" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B198" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C198" t="s">
         <v>255</v>
@@ -3085,7 +3088,7 @@
     </row>
     <row r="199" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B199" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C199" t="s">
         <v>255</v>
@@ -3093,7 +3096,7 @@
     </row>
     <row r="200" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B200" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C200" t="s">
         <v>255</v>
@@ -3101,7 +3104,7 @@
     </row>
     <row r="201" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B201" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C201" t="s">
         <v>255</v>
@@ -3109,7 +3112,7 @@
     </row>
     <row r="202" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B202" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C202" t="s">
         <v>255</v>
@@ -3117,7 +3120,7 @@
     </row>
     <row r="203" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B203" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C203" t="s">
         <v>255</v>
@@ -3125,7 +3128,7 @@
     </row>
     <row r="204" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B204" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C204" t="s">
         <v>255</v>
@@ -3133,7 +3136,7 @@
     </row>
     <row r="205" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B205" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C205" t="s">
         <v>255</v>
@@ -3141,7 +3144,7 @@
     </row>
     <row r="206" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B206" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C206" t="s">
         <v>255</v>
@@ -3149,7 +3152,7 @@
     </row>
     <row r="207" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B207" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C207" t="s">
         <v>255</v>
@@ -3157,7 +3160,7 @@
     </row>
     <row r="208" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B208" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C208" t="s">
         <v>255</v>
@@ -3165,7 +3168,7 @@
     </row>
     <row r="209" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B209" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C209" t="s">
         <v>255</v>
@@ -3173,9 +3176,17 @@
     </row>
     <row r="210" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B210" t="s">
+        <v>209</v>
+      </c>
+      <c r="C210" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="211" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B211" t="s">
         <v>210</v>
       </c>
-      <c r="C210" t="s">
+      <c r="C211" t="s">
         <v>255</v>
       </c>
     </row>

--- a/config/Amazon_instruction.xlsx
+++ b/config/Amazon_instruction.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\our data\KPA\NEW\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A29E8DFD-6288-4B3D-A453-48FAF6AE9BEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A58888B1-6675-4A8A-A113-FC093803964A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="262">
   <si>
     <t>Base file Column</t>
   </si>
@@ -810,13 +810,28 @@
   </si>
   <si>
     <t>item_booking_date#1.value</t>
+  </si>
+  <si>
+    <t>Bullet Point1</t>
+  </si>
+  <si>
+    <t>Bullet Point2</t>
+  </si>
+  <si>
+    <t>Bullet Point3</t>
+  </si>
+  <si>
+    <t>Bullet Point4</t>
+  </si>
+  <si>
+    <t>Bullet Point5</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -824,13 +839,27 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -845,8 +874,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1509,6 +1541,9 @@
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A37" s="1" t="s">
+        <v>257</v>
+      </c>
       <c r="B37" t="s">
         <v>38</v>
       </c>
@@ -1517,6 +1552,9 @@
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A38" s="1" t="s">
+        <v>258</v>
+      </c>
       <c r="B38" t="s">
         <v>39</v>
       </c>
@@ -1525,6 +1563,9 @@
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A39" s="1" t="s">
+        <v>259</v>
+      </c>
       <c r="B39" t="s">
         <v>40</v>
       </c>
@@ -1533,6 +1574,9 @@
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A40" s="1" t="s">
+        <v>260</v>
+      </c>
       <c r="B40" t="s">
         <v>41</v>
       </c>
@@ -1541,6 +1585,9 @@
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A41" s="1" t="s">
+        <v>261</v>
+      </c>
       <c r="B41" t="s">
         <v>42</v>
       </c>

--- a/config/Amazon_instruction.xlsx
+++ b/config/Amazon_instruction.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\our data\KPA\NEW\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A58888B1-6675-4A8A-A113-FC093803964A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{417B2973-3B64-4C76-9F90-54655470731E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="262">
   <si>
     <t>Base file Column</t>
   </si>
@@ -1797,6 +1797,9 @@
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>231</v>
+      </c>
       <c r="B60" t="s">
         <v>61</v>
       </c>

--- a/config/Amazon_instruction.xlsx
+++ b/config/Amazon_instruction.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\our data\KPA\NEW\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{417B2973-3B64-4C76-9F90-54655470731E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0E936E4-6157-4216-8CB6-855BF56C0B73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="551" uniqueCount="262">
   <si>
     <t>Base file Column</t>
   </si>
@@ -1806,6 +1806,9 @@
       <c r="C60" t="s">
         <v>255</v>
       </c>
+      <c r="D60" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61" t="s">

--- a/config/Amazon_instruction.xlsx
+++ b/config/Amazon_instruction.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\our data\KPA\NEW\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0E936E4-6157-4216-8CB6-855BF56C0B73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E35974B-3F8E-4761-A46D-87F22626E4DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="551" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="261">
   <si>
     <t>Base file Column</t>
   </si>
@@ -48,9 +48,6 @@
   </si>
   <si>
     <t>Remarks</t>
-  </si>
-  <si>
-    <t>rtip_vendor_code#1.value</t>
   </si>
   <si>
     <t>vendor_sku#1.value</t>
@@ -1159,7 +1156,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E211"/>
+  <dimension ref="A1:E209"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.7265625" bestFit="1" customWidth="1"/>
@@ -1173,7 +1170,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -1182,89 +1179,92 @@
         <v>2</v>
       </c>
       <c r="E1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>211</v>
+      </c>
       <c r="B2" t="s">
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>212</v>
+        <v>1</v>
       </c>
       <c r="B3" t="s">
         <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>255</v>
+        <v>254</v>
+      </c>
+      <c r="D3" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>1</v>
+        <v>212</v>
       </c>
       <c r="B4" t="s">
         <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>255</v>
-      </c>
-      <c r="D4" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>213</v>
+        <v>1</v>
       </c>
       <c r="B5" t="s">
         <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>255</v>
+        <v>254</v>
+      </c>
+      <c r="D5" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>1</v>
+        <v>213</v>
       </c>
       <c r="B6" t="s">
         <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>255</v>
-      </c>
-      <c r="D6" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>214</v>
+        <v>1</v>
       </c>
       <c r="B7" t="s">
         <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>255</v>
+        <v>254</v>
+      </c>
+      <c r="D7" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>1</v>
+        <v>214</v>
       </c>
       <c r="B8" t="s">
         <v>9</v>
       </c>
       <c r="C8" t="s">
-        <v>255</v>
-      </c>
-      <c r="D8" t="s">
         <v>254</v>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
         <v>10</v>
       </c>
       <c r="C9" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
@@ -1287,20 +1287,17 @@
         <v>11</v>
       </c>
       <c r="C10" t="s">
-        <v>255</v>
+        <v>254</v>
+      </c>
+      <c r="D10" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>217</v>
-      </c>
       <c r="B11" t="s">
         <v>12</v>
       </c>
       <c r="C11" t="s">
-        <v>255</v>
-      </c>
-      <c r="D11" t="s">
         <v>254</v>
       </c>
     </row>
@@ -1309,7 +1306,7 @@
         <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
@@ -1317,7 +1314,7 @@
         <v>14</v>
       </c>
       <c r="C13" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
@@ -1325,7 +1322,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
@@ -1333,7 +1330,7 @@
         <v>16</v>
       </c>
       <c r="C15" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
@@ -1341,7 +1338,7 @@
         <v>17</v>
       </c>
       <c r="C16" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
@@ -1349,7 +1346,7 @@
         <v>18</v>
       </c>
       <c r="C17" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
@@ -1357,7 +1354,7 @@
         <v>19</v>
       </c>
       <c r="C18" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
@@ -1365,7 +1362,7 @@
         <v>20</v>
       </c>
       <c r="C19" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
@@ -1373,7 +1370,7 @@
         <v>21</v>
       </c>
       <c r="C20" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
@@ -1381,7 +1378,7 @@
         <v>22</v>
       </c>
       <c r="C21" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
@@ -1389,26 +1386,29 @@
         <v>23</v>
       </c>
       <c r="C22" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>213</v>
+      </c>
       <c r="B23" t="s">
         <v>24</v>
       </c>
       <c r="C23" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B24" t="s">
         <v>25</v>
       </c>
       <c r="C24" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
@@ -1419,7 +1419,7 @@
         <v>26</v>
       </c>
       <c r="C25" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
@@ -1430,7 +1430,7 @@
         <v>27</v>
       </c>
       <c r="C26" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
@@ -1441,7 +1441,7 @@
         <v>28</v>
       </c>
       <c r="C27" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
@@ -1452,7 +1452,7 @@
         <v>29</v>
       </c>
       <c r="C28" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
@@ -1463,7 +1463,7 @@
         <v>30</v>
       </c>
       <c r="C29" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
@@ -1474,7 +1474,7 @@
         <v>31</v>
       </c>
       <c r="C30" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
@@ -1485,7 +1485,7 @@
         <v>32</v>
       </c>
       <c r="C31" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
@@ -1496,7 +1496,7 @@
         <v>33</v>
       </c>
       <c r="C32" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
@@ -1507,7 +1507,7 @@
         <v>34</v>
       </c>
       <c r="C33" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
@@ -1518,26 +1518,26 @@
         <v>35</v>
       </c>
       <c r="C34" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
-        <v>228</v>
-      </c>
       <c r="B35" t="s">
         <v>36</v>
       </c>
       <c r="C35" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>256</v>
+      </c>
       <c r="B36" t="s">
         <v>37</v>
       </c>
       <c r="C36" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
@@ -1548,7 +1548,7 @@
         <v>38</v>
       </c>
       <c r="C37" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
@@ -1559,7 +1559,7 @@
         <v>39</v>
       </c>
       <c r="C38" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
@@ -1570,7 +1570,7 @@
         <v>40</v>
       </c>
       <c r="C39" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
@@ -1581,42 +1581,39 @@
         <v>41</v>
       </c>
       <c r="C40" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
-        <v>261</v>
+        <v>228</v>
       </c>
       <c r="B41" t="s">
         <v>42</v>
       </c>
       <c r="C41" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>229</v>
+        <v>1</v>
       </c>
       <c r="B42" t="s">
         <v>43</v>
       </c>
       <c r="C42" t="s">
-        <v>255</v>
+        <v>254</v>
+      </c>
+      <c r="D42" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A43" t="s">
-        <v>1</v>
-      </c>
       <c r="B43" t="s">
         <v>44</v>
       </c>
       <c r="C43" t="s">
-        <v>255</v>
-      </c>
-      <c r="D43" t="s">
         <v>254</v>
       </c>
     </row>
@@ -1625,7 +1622,7 @@
         <v>45</v>
       </c>
       <c r="C44" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
@@ -1633,7 +1630,7 @@
         <v>46</v>
       </c>
       <c r="C45" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
@@ -1641,28 +1638,28 @@
         <v>47</v>
       </c>
       <c r="C46" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>1</v>
+      </c>
       <c r="B47" t="s">
         <v>48</v>
       </c>
       <c r="C47" t="s">
-        <v>255</v>
+        <v>254</v>
+      </c>
+      <c r="D47" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A48" t="s">
-        <v>1</v>
-      </c>
       <c r="B48" t="s">
         <v>49</v>
       </c>
       <c r="C48" t="s">
-        <v>255</v>
-      </c>
-      <c r="D48" t="s">
         <v>254</v>
       </c>
     </row>
@@ -1671,7 +1668,7 @@
         <v>50</v>
       </c>
       <c r="C49" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
@@ -1679,7 +1676,7 @@
         <v>51</v>
       </c>
       <c r="C50" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
@@ -1687,85 +1684,91 @@
         <v>52</v>
       </c>
       <c r="C51" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>1</v>
+      </c>
       <c r="B52" t="s">
         <v>53</v>
       </c>
       <c r="C52" t="s">
-        <v>255</v>
+        <v>254</v>
+      </c>
+      <c r="D52" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>1</v>
+        <v>229</v>
       </c>
       <c r="B53" t="s">
         <v>54</v>
       </c>
       <c r="C53" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D53" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B54" t="s">
         <v>55</v>
       </c>
       <c r="C54" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D54" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B55" t="s">
         <v>56</v>
       </c>
       <c r="C55" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D55" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B56" t="s">
         <v>57</v>
       </c>
       <c r="C56" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D56" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B57" t="s">
         <v>58</v>
       </c>
       <c r="C57" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D57" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.35">
@@ -1776,65 +1779,59 @@
         <v>59</v>
       </c>
       <c r="C58" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D58" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B59" t="s">
         <v>60</v>
       </c>
       <c r="C59" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D59" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>231</v>
+        <v>1</v>
       </c>
       <c r="B60" t="s">
         <v>61</v>
       </c>
       <c r="C60" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D60" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>1</v>
+        <v>231</v>
       </c>
       <c r="B61" t="s">
         <v>62</v>
       </c>
       <c r="C61" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D61" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A62" t="s">
-        <v>232</v>
-      </c>
       <c r="B62" t="s">
         <v>63</v>
       </c>
       <c r="C62" t="s">
-        <v>255</v>
-      </c>
-      <c r="D62" t="s">
         <v>254</v>
       </c>
     </row>
@@ -1843,15 +1840,18 @@
         <v>64</v>
       </c>
       <c r="C63" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>231</v>
+      </c>
       <c r="B64" t="s">
         <v>65</v>
       </c>
       <c r="C64" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.35">
@@ -1862,7 +1862,7 @@
         <v>66</v>
       </c>
       <c r="C65" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.35">
@@ -1873,7 +1873,10 @@
         <v>67</v>
       </c>
       <c r="C66" t="s">
-        <v>255</v>
+        <v>254</v>
+      </c>
+      <c r="D66" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.35">
@@ -1884,34 +1887,31 @@
         <v>68</v>
       </c>
       <c r="C67" t="s">
-        <v>255</v>
-      </c>
-      <c r="D67" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>235</v>
+        <v>1</v>
       </c>
       <c r="B68" t="s">
         <v>69</v>
       </c>
       <c r="C68" t="s">
-        <v>255</v>
+        <v>254</v>
+      </c>
+      <c r="D68" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>1</v>
+        <v>235</v>
       </c>
       <c r="B69" t="s">
         <v>70</v>
       </c>
       <c r="C69" t="s">
-        <v>255</v>
-      </c>
-      <c r="D69" t="s">
         <v>254</v>
       </c>
     </row>
@@ -1923,7 +1923,10 @@
         <v>71</v>
       </c>
       <c r="C70" t="s">
-        <v>255</v>
+        <v>254</v>
+      </c>
+      <c r="D70" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.35">
@@ -1934,9 +1937,6 @@
         <v>72</v>
       </c>
       <c r="C71" t="s">
-        <v>255</v>
-      </c>
-      <c r="D71" t="s">
         <v>254</v>
       </c>
     </row>
@@ -1948,7 +1948,10 @@
         <v>73</v>
       </c>
       <c r="C72" t="s">
-        <v>255</v>
+        <v>254</v>
+      </c>
+      <c r="D72" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.35">
@@ -1959,157 +1962,157 @@
         <v>74</v>
       </c>
       <c r="C73" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B74" t="s">
         <v>255</v>
       </c>
-      <c r="D73" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A74" t="s">
-        <v>240</v>
-      </c>
-      <c r="B74" t="s">
-        <v>75</v>
-      </c>
       <c r="C74" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B75" t="s">
-        <v>256</v>
+        <v>75</v>
       </c>
       <c r="C75" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A76" t="s">
-        <v>241</v>
-      </c>
       <c r="B76" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C76" t="s">
-        <v>255</v>
-      </c>
-      <c r="D76" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B77" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C77" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B78" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C78" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B79" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C79" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
+        <v>240</v>
+      </c>
       <c r="B80" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C80" t="s">
-        <v>255</v>
+        <v>254</v>
+      </c>
+      <c r="D80" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B81" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C81" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
+        <v>241</v>
+      </c>
       <c r="B82" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C82" t="s">
-        <v>255</v>
+        <v>254</v>
+      </c>
+      <c r="D82" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
+        <v>218</v>
+      </c>
       <c r="B83" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C83" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A84" t="s">
-        <v>242</v>
-      </c>
       <c r="B84" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C84" t="s">
-        <v>255</v>
-      </c>
-      <c r="D84" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="B85" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C85" t="s">
-        <v>255</v>
+        <v>254</v>
+      </c>
+      <c r="D85" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
+        <v>232</v>
+      </c>
       <c r="B86" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C86" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>243</v>
+        <v>1</v>
       </c>
       <c r="B87" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C87" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D87" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A88" t="s">
-        <v>233</v>
-      </c>
       <c r="B88" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C88" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.35">
@@ -2117,649 +2120,652 @@
         <v>1</v>
       </c>
       <c r="B89" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C89" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D89" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B90" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C90" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A91" t="s">
-        <v>1</v>
-      </c>
       <c r="B91" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C91" t="s">
-        <v>255</v>
-      </c>
-      <c r="D91" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B92" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C92" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B93" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C93" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B94" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C94" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B95" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C95" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B96" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C96" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B97" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C97" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B98" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C98" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B99" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C99" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B100" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C100" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B101" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C101" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A102" t="s">
+        <v>1</v>
+      </c>
       <c r="B102" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C102" t="s">
-        <v>255</v>
+        <v>254</v>
+      </c>
+      <c r="D102" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A103" t="s">
+        <v>243</v>
+      </c>
       <c r="B103" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C103" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A104" t="s">
-        <v>1</v>
-      </c>
       <c r="B104" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C104" t="s">
-        <v>255</v>
-      </c>
-      <c r="D104" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A105" t="s">
-        <v>244</v>
-      </c>
       <c r="B105" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C105" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B106" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C106" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B107" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C107" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B108" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C108" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A109" t="s">
+        <v>244</v>
+      </c>
       <c r="B109" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C109" t="s">
-        <v>255</v>
+        <v>254</v>
+      </c>
+      <c r="D109" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B110" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C110" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A111" t="s">
-        <v>245</v>
-      </c>
       <c r="B111" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C111" t="s">
-        <v>255</v>
-      </c>
-      <c r="D111" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B112" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C112" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B113" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C113" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B114" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C114" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B115" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C115" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B116" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C116" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B117" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C117" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B118" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C118" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A119" t="s">
+        <v>1</v>
+      </c>
       <c r="B119" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C119" t="s">
-        <v>255</v>
+        <v>254</v>
+      </c>
+      <c r="D119" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A120" t="s">
+        <v>1</v>
+      </c>
       <c r="B120" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C120" t="s">
-        <v>255</v>
+        <v>254</v>
+      </c>
+      <c r="D120" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A121" t="s">
-        <v>1</v>
-      </c>
       <c r="B121" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C121" t="s">
-        <v>255</v>
-      </c>
-      <c r="D121" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A122" t="s">
-        <v>1</v>
-      </c>
       <c r="B122" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C122" t="s">
-        <v>255</v>
-      </c>
-      <c r="D122" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B123" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C123" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B124" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C124" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B125" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C125" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B126" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C126" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A127" t="s">
+        <v>218</v>
+      </c>
       <c r="B127" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C127" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B128" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C128" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A129" t="s">
-        <v>219</v>
-      </c>
       <c r="B129" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C129" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B130" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C130" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B131" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C131" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B132" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C132" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A133" t="s">
+        <v>1</v>
+      </c>
       <c r="B133" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C133" t="s">
-        <v>255</v>
+        <v>254</v>
+      </c>
+      <c r="D133" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B134" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C134" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A135" t="s">
-        <v>1</v>
-      </c>
       <c r="B135" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C135" t="s">
-        <v>255</v>
-      </c>
-      <c r="D135" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A136" t="s">
+        <v>245</v>
+      </c>
       <c r="B136" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C136" t="s">
-        <v>255</v>
+        <v>254</v>
+      </c>
+      <c r="D136" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B137" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C137" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>246</v>
+        <v>1</v>
       </c>
       <c r="B138" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C138" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D138" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B139" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C139" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A140" t="s">
-        <v>1</v>
-      </c>
       <c r="B140" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C140" t="s">
-        <v>255</v>
-      </c>
-      <c r="D140" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B141" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C141" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B142" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C142" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B143" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C143" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B144" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C144" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.35">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B145" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C145" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.35">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B146" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C146" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.35">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B147" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C147" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.35">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B148" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C148" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.35">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B149" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C149" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.35">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B150" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C150" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.35">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B151" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C151" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.35">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B152" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C152" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.35">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B153" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C153" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.35">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B154" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C154" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.35">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B155" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C155" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.35">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A156" t="s">
+        <v>250</v>
+      </c>
       <c r="B156" t="s">
-        <v>155</v>
+        <v>176</v>
       </c>
       <c r="C156" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.35">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A157" t="s">
+        <v>1</v>
+      </c>
       <c r="B157" t="s">
+        <v>177</v>
+      </c>
+      <c r="C157" t="s">
+        <v>254</v>
+      </c>
+      <c r="D157" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A158" t="s">
+        <v>246</v>
+      </c>
+      <c r="B158" t="s">
         <v>156</v>
       </c>
-      <c r="C157" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A158" t="s">
-        <v>247</v>
-      </c>
-      <c r="B158" t="s">
+      <c r="C158" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B159" t="s">
         <v>157</v>
       </c>
-      <c r="C158" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B159" t="s">
+      <c r="C159" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B160" t="s">
         <v>158</v>
       </c>
-      <c r="C159" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B160" t="s">
-        <v>159</v>
-      </c>
       <c r="C160" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B161" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C161" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.35">
@@ -2767,24 +2773,24 @@
         <v>1</v>
       </c>
       <c r="B162" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C162" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D162" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B163" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C163" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.35">
@@ -2792,24 +2798,24 @@
         <v>1</v>
       </c>
       <c r="B164" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C164" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D164" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B165" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C165" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.35">
@@ -2817,24 +2823,24 @@
         <v>1</v>
       </c>
       <c r="B166" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C166" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D166" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B167" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C167" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.35">
@@ -2842,24 +2848,24 @@
         <v>1</v>
       </c>
       <c r="B168" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C168" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D168" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B169" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C169" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.35">
@@ -2867,24 +2873,24 @@
         <v>1</v>
       </c>
       <c r="B170" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C170" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D170" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B171" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C171" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.35">
@@ -2892,24 +2898,24 @@
         <v>1</v>
       </c>
       <c r="B172" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C172" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D172" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B173" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C173" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.35">
@@ -2917,13 +2923,13 @@
         <v>1</v>
       </c>
       <c r="B174" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C174" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D174" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.35">
@@ -2931,316 +2937,291 @@
         <v>1</v>
       </c>
       <c r="B175" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C175" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D175" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B176" t="s">
+        <v>174</v>
+      </c>
+      <c r="C176" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A177" t="s">
+        <v>251</v>
+      </c>
+      <c r="B177" t="s">
         <v>175</v>
       </c>
-      <c r="C176" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A177" t="s">
-        <v>252</v>
-      </c>
-      <c r="B177" t="s">
-        <v>176</v>
-      </c>
       <c r="C177" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A178" t="s">
-        <v>251</v>
-      </c>
+        <v>254</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B178" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C178" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A179" t="s">
-        <v>1</v>
-      </c>
+        <v>254</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B179" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C179" t="s">
-        <v>255</v>
-      </c>
-      <c r="D179" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.35">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B180" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C180" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.35">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B181" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C181" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.35">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B182" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C182" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.35">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B183" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C183" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.35">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B184" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C184" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.35">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B185" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C185" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.35">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B186" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C186" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.35">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B187" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C187" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.35">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B188" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C188" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.35">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B189" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C189" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.35">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B190" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C190" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.35">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B191" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C191" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.35">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B192" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C192" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="193" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B193" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C193" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="194" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B194" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C194" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="195" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B195" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C195" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="196" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B196" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C196" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="197" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B197" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C197" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="198" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B198" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C198" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="199" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B199" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C199" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="200" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B200" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C200" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="201" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B201" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C201" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="202" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B202" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C202" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="203" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B203" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C203" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="204" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B204" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C204" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="205" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B205" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C205" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="206" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B206" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C206" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="207" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B207" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C207" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="208" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B208" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C208" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="209" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B209" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C209" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="210" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B210" t="s">
-        <v>209</v>
-      </c>
-      <c r="C210" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="211" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B211" t="s">
-        <v>210</v>
-      </c>
-      <c r="C211" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
   </sheetData>
